--- a/artfynd/A 19666-2026 artfynd.xlsx
+++ b/artfynd/A 19666-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AY8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,57 +675,48 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119846662</v>
+        <v>89045228</v>
       </c>
       <c r="B2" t="n">
-        <v>97930</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Mörtkullnäset, Ång</t>
+          <t>Hällnäset, 2 km SO om, Ång</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>554225</v>
+        <v>554250</v>
       </c>
       <c r="R2" t="n">
-        <v>7087514</v>
+        <v>7087623</v>
       </c>
       <c r="S2" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -749,12 +740,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
+          <t>2020-06-17</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
+          <t>2020-06-17</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -763,56 +754,67 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
+      </c>
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>naturskogsartad blåbärsgranskog mot sumpskog</t>
+        </is>
+      </c>
+      <c r="AN2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>1 substratenheter # äldre granlåga</t>
+        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Maria Johansson</t>
+          <t>Magnus Andersson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Maria Johansson</t>
-        </is>
-      </c>
-      <c r="AY2" t="inlineStr"/>
+          <t>Magnus Andersson</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr">
+        <is>
+          <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119846679</v>
+        <v>119846664</v>
       </c>
       <c r="B3" t="n">
-        <v>74654</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -825,10 +827,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>554254</v>
+        <v>554226</v>
       </c>
       <c r="R3" t="n">
-        <v>7087525</v>
+        <v>7087512</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -888,15 +890,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119846711</v>
+        <v>119846679</v>
       </c>
       <c r="B4" t="n">
-        <v>78278</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83307</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -904,21 +901,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6446</v>
+        <v>6440</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -931,10 +928,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>554455</v>
+        <v>554254</v>
       </c>
       <c r="R4" t="n">
-        <v>7087262</v>
+        <v>7087525</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -994,15 +991,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119846664</v>
+        <v>119846711</v>
       </c>
       <c r="B5" t="n">
-        <v>78542</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79084</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1010,21 +1002,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1037,10 +1029,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>554226</v>
+        <v>554455</v>
       </c>
       <c r="R5" t="n">
-        <v>7087512</v>
+        <v>7087262</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1100,15 +1092,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119846668</v>
+        <v>119846630</v>
       </c>
       <c r="B6" t="n">
-        <v>79623</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1143,10 +1130,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>554219</v>
+        <v>554279</v>
       </c>
       <c r="R6" t="n">
-        <v>7087504</v>
+        <v>7087387</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1203,6 +1190,209 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>119846668</v>
+      </c>
+      <c r="B7" t="n">
+        <v>80432</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Mörtkullnäset, Ång</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>554219</v>
+      </c>
+      <c r="R7" t="n">
+        <v>7087504</v>
+      </c>
+      <c r="S7" t="n">
+        <v>25</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Fjällsjö</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2024-09-18</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2024-09-18</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF7" t="inlineStr"/>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Maria Johansson</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Maria Johansson</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>119846662</v>
+      </c>
+      <c r="B8" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Mörtkullnäset, Ång</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>554225</v>
+      </c>
+      <c r="R8" t="n">
+        <v>7087514</v>
+      </c>
+      <c r="S8" t="n">
+        <v>25</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Fjällsjö</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2024-09-18</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2024-09-18</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF8" t="inlineStr"/>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Maria Johansson</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Maria Johansson</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 19666-2026 artfynd.xlsx
+++ b/artfynd/A 19666-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY8"/>
+  <dimension ref="A1:AZ8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -784,6 +789,11 @@
       <c r="AY2" t="inlineStr">
         <is>
           <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89045228</t>
         </is>
       </c>
     </row>
@@ -887,6 +897,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119846664</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -988,6 +1003,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119846679</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1089,6 +1109,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119846711</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1190,6 +1215,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119846630</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1291,6 +1321,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119846668</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1393,8 +1428,22 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119846662</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>